--- a/page_passage_source/facebook.xlsx
+++ b/page_passage_source/facebook.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kulu/Desktop/PhD/Research/AIGC_Social_Media/dataset(organization_needed)/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kulu/Desktop/PhD/Research/AIGC_Social_Media/final_dataset/page_passage_source/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16B81C65-6E9E-DA47-8C93-CCD8D88C7AFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F04E75DC-F2DD-8042-AFF5-38DFAC40495D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="34560" windowHeight="19940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4840" yWindow="500" windowWidth="34560" windowHeight="19920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -302,9 +302,6 @@
 </t>
   </si>
   <si>
-    <t>https://www.facebook.com/help/7745061278859290/?cms_platform=iphone-app&amp;helpref=platform_switcher&amp;_rdr</t>
-  </si>
-  <si>
     <t>Write with AI on Facebook |
 Facebook Help Center Help Center English (US) Using Facebook Login, Recovery and Security Managing Your Account Privacy and Safety Policies and Reporting Write with AI on Facebook iPhone App Help Android App Help More iPhone App Help
 Android App Help Writing with AI on Facebook isn't yet available for everyone.
@@ -332,9 +329,6 @@
 Learn more about how Meta uses information for generative AI models .
 Was this helpful?
 … Yes No Related Articles Ask Meta AI on Facebook Use voice with Meta AI on Facebook Have an AI remember details about you while chatting on Facebook Have Meta AI remember details about you while chatting on Facebook Chat with a custom AI on Facebook Related Articles Ask Meta AI on Facebook Use voice with Meta AI on Facebook Have an AI remember details about you while chatting on Facebook Have Meta AI remember details about you while chatting on Facebook Chat with a custom AI on Facebook About Privacy Terms and Policies Ad Choices Careers Cookies Create Ad Create Page © 2025 Meta Feedback</t>
-  </si>
-  <si>
-    <t>https://www.facebook.com/help/7434563519957988/?cms_platform=iphone-app&amp;helpref=platform_switcher</t>
   </si>
   <si>
     <t>Label AI content on Facebook | Facebook Help Center Help Center English (US) Using Facebook Login, Recovery and Security Managing Your Account Privacy and Safety Policies and Reporting Label AI content on Facebook Android App Help iPhone App Help More Android App Help iPhone App Help Labeling and identifying AI content is different for ads.
@@ -1896,9 +1890,6 @@
 Sign up By signing up you agree to receive updates and marketing messages (e.g. email, social, etc.) from Meta about Meta’s existing and future products and services.</t>
   </si>
   <si>
-    <t>https://www.facebook.com/help/1031349015172367?cms_platform=iphone-app</t>
-  </si>
-  <si>
     <t>Generate images with Meta AI on Facebook | Facebook Help Center Help Center English (US) Using Facebook Login, Recovery and Security Managing Your Account Privacy and Safety Policies Reporting Generate images with Meta AI on Facebook iPhone App Help Android App Help More iPhone App Help
 Android App Help
 This feature is being gradually introduced and may not be available to you yet.
@@ -2046,6 +2037,15 @@
   </si>
   <si>
     <t>passage_type</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/help/7745061278859290</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/help/7434563519957988</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/help/1031349015172367</t>
   </si>
 </sst>
 </file>
@@ -2445,25 +2445,25 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>129</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>132</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="409.6" x14ac:dyDescent="0.2">
@@ -2483,10 +2483,10 @@
         <v>3</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="409.6" x14ac:dyDescent="0.2">
@@ -2500,16 +2500,16 @@
         <v>4</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="409.6" x14ac:dyDescent="0.2">
@@ -2523,16 +2523,16 @@
         <v>6</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>7</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="409.6" x14ac:dyDescent="0.2">
@@ -2546,16 +2546,16 @@
         <v>8</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>9</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="409.6" x14ac:dyDescent="0.2">
@@ -2575,10 +2575,10 @@
         <v>11</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="409.6" x14ac:dyDescent="0.2">
@@ -2589,19 +2589,19 @@
         <v>6</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>12</v>
+        <v>130</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="409.6" x14ac:dyDescent="0.2">
@@ -2612,19 +2612,19 @@
         <v>7</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>14</v>
+        <v>131</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="409.6" x14ac:dyDescent="0.2">
@@ -2635,19 +2635,19 @@
         <v>8</v>
       </c>
       <c r="C9" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E9" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D9" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="F9" s="1" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="409.6" x14ac:dyDescent="0.2">
@@ -2658,19 +2658,19 @@
         <v>9</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="409.6" x14ac:dyDescent="0.2">
@@ -2681,19 +2681,19 @@
         <v>10</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>2</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="409.6" x14ac:dyDescent="0.2">
@@ -2704,19 +2704,19 @@
         <v>11</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>2</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="409.6" x14ac:dyDescent="0.2">
@@ -2727,19 +2727,19 @@
         <v>12</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>2</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="409.6" x14ac:dyDescent="0.2">
@@ -2750,19 +2750,19 @@
         <v>13</v>
       </c>
       <c r="C14" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E14" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D14" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="F14" s="1" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="409.6" x14ac:dyDescent="0.2">
@@ -2773,19 +2773,19 @@
         <v>14</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="409.6" x14ac:dyDescent="0.2">
@@ -2796,19 +2796,19 @@
         <v>15</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="409.6" x14ac:dyDescent="0.2">
@@ -2819,19 +2819,19 @@
         <v>16</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="409.6" x14ac:dyDescent="0.2">
@@ -2842,19 +2842,19 @@
         <v>17</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="409.6" x14ac:dyDescent="0.2">
@@ -2865,19 +2865,19 @@
         <v>18</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>2</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="409.6" x14ac:dyDescent="0.2">
@@ -2888,19 +2888,19 @@
         <v>18</v>
       </c>
       <c r="C20" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E20" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D20" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>39</v>
-      </c>
       <c r="F20" s="1" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="409.6" x14ac:dyDescent="0.2">
@@ -2911,19 +2911,19 @@
         <v>19</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="409.6" x14ac:dyDescent="0.2">
@@ -2934,19 +2934,19 @@
         <v>19</v>
       </c>
       <c r="C22" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E22" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D22" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>42</v>
-      </c>
       <c r="F22" s="1" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="409.6" x14ac:dyDescent="0.2">
@@ -2957,19 +2957,19 @@
         <v>19</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="409.6" x14ac:dyDescent="0.2">
@@ -2980,19 +2980,19 @@
         <v>19</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="409.6" x14ac:dyDescent="0.2">
@@ -3003,19 +3003,19 @@
         <v>20</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>2</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="26" spans="1:7" ht="409.6" x14ac:dyDescent="0.2">
@@ -3026,19 +3026,19 @@
         <v>20</v>
       </c>
       <c r="C26" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E26" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D26" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>47</v>
-      </c>
       <c r="F26" s="1" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="409.6" x14ac:dyDescent="0.2">
@@ -3049,19 +3049,19 @@
         <v>21</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D27" s="1" t="s">
         <v>2</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="28" spans="1:7" ht="409.6" x14ac:dyDescent="0.2">
@@ -3072,19 +3072,19 @@
         <v>22</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="29" spans="1:7" ht="409.6" x14ac:dyDescent="0.2">
@@ -3095,19 +3095,19 @@
         <v>23</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="30" spans="1:7" ht="409.6" x14ac:dyDescent="0.2">
@@ -3118,19 +3118,19 @@
         <v>24</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="31" spans="1:7" ht="409.6" x14ac:dyDescent="0.2">
@@ -3141,19 +3141,19 @@
         <v>25</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="32" spans="1:7" ht="409.6" x14ac:dyDescent="0.2">
@@ -3164,7 +3164,7 @@
         <v>26</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D32" s="1" t="s">
         <v>2</v>
@@ -3173,10 +3173,10 @@
         <v>3</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="33" spans="1:7" ht="409.6" x14ac:dyDescent="0.2">
@@ -3187,19 +3187,19 @@
         <v>27</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D33" s="1" t="s">
         <v>2</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="34" spans="1:7" ht="409.6" x14ac:dyDescent="0.2">
@@ -3210,19 +3210,19 @@
         <v>28</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D34" s="1" t="s">
         <v>2</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="35" spans="1:7" ht="409.6" x14ac:dyDescent="0.2">
@@ -3233,19 +3233,19 @@
         <v>29</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D35" s="1" t="s">
         <v>2</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="36" spans="1:7" ht="409.6" x14ac:dyDescent="0.2">
@@ -3256,19 +3256,19 @@
         <v>30</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="37" spans="1:7" ht="409.6" x14ac:dyDescent="0.2">
@@ -3279,19 +3279,19 @@
         <v>30</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D37" s="1" t="s">
         <v>2</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="38" spans="1:7" ht="409.6" x14ac:dyDescent="0.2">
@@ -3302,19 +3302,19 @@
         <v>31</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
     <row r="39" spans="1:7" ht="409.6" x14ac:dyDescent="0.2">
@@ -3325,19 +3325,19 @@
         <v>31</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D39" s="1" t="s">
         <v>2</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="40" spans="1:7" ht="409.6" x14ac:dyDescent="0.2">
@@ -3348,19 +3348,19 @@
         <v>32</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D40" s="1" t="s">
         <v>2</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="41" spans="1:7" ht="409.6" x14ac:dyDescent="0.2">
@@ -3371,19 +3371,19 @@
         <v>33</v>
       </c>
       <c r="C41" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="E41" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D41" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="E41" s="1" t="s">
-        <v>74</v>
-      </c>
       <c r="F41" s="1" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="42" spans="1:7" ht="409.6" x14ac:dyDescent="0.2">
@@ -3394,19 +3394,19 @@
         <v>34</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="43" spans="1:7" ht="409.6" x14ac:dyDescent="0.2">
@@ -3417,19 +3417,19 @@
         <v>35</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D43" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="F43" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="E43" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="F43" s="1" t="s">
-        <v>122</v>
-      </c>
       <c r="G43" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="44" spans="1:7" ht="409.6" x14ac:dyDescent="0.2">
@@ -3440,19 +3440,19 @@
         <v>36</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="45" spans="1:7" ht="409.6" x14ac:dyDescent="0.2">
@@ -3463,19 +3463,19 @@
         <v>37</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D45" s="1" t="s">
         <v>2</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="46" spans="1:7" ht="409.6" x14ac:dyDescent="0.2">
@@ -3486,19 +3486,19 @@
         <v>38</v>
       </c>
       <c r="C46" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E46" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D46" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="E46" s="1" t="s">
-        <v>85</v>
-      </c>
       <c r="F46" s="1" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="47" spans="1:7" ht="409.6" x14ac:dyDescent="0.2">
@@ -3509,19 +3509,19 @@
         <v>39</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D47" s="1" t="s">
         <v>2</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="48" spans="1:7" ht="409.6" x14ac:dyDescent="0.2">
@@ -3532,19 +3532,19 @@
         <v>40</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="49" spans="1:7" ht="409.6" x14ac:dyDescent="0.2">
@@ -3555,19 +3555,19 @@
         <v>40</v>
       </c>
       <c r="C49" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="E49" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="D49" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="E49" s="1" t="s">
-        <v>90</v>
-      </c>
       <c r="F49" s="1" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="50" spans="1:7" ht="409.6" x14ac:dyDescent="0.2">
@@ -3578,19 +3578,19 @@
         <v>41</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="51" spans="1:7" ht="409.6" x14ac:dyDescent="0.2">
@@ -3601,19 +3601,19 @@
         <v>42</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="52" spans="1:7" ht="409.6" x14ac:dyDescent="0.2">
@@ -3624,19 +3624,19 @@
         <v>42</v>
       </c>
       <c r="C52" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E52" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="D52" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E52" s="1" t="s">
-        <v>95</v>
-      </c>
       <c r="F52" s="1" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="53" spans="1:7" ht="409.6" x14ac:dyDescent="0.2">
@@ -3647,19 +3647,19 @@
         <v>42</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="54" spans="1:7" ht="409.6" x14ac:dyDescent="0.2">
@@ -3670,19 +3670,19 @@
         <v>43</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="55" spans="1:7" ht="409.6" x14ac:dyDescent="0.2">
@@ -3693,19 +3693,19 @@
         <v>44</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D55" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="E55" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="F55" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="E55" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="F55" s="1" t="s">
-        <v>124</v>
-      </c>
       <c r="G55" s="1" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
     <row r="56" spans="1:7" ht="409.6" x14ac:dyDescent="0.2">
@@ -3716,19 +3716,19 @@
         <v>45</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>101</v>
+        <v>132</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="57" spans="1:7" ht="409.6" x14ac:dyDescent="0.2">
@@ -3739,19 +3739,19 @@
         <v>46</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
   </sheetData>
